--- a/results/models/coverage_v12_SA_ELECTRE_InfrastructureFocused_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
+++ b/results/models/coverage_v12_SA_ELECTRE_InfrastructureFocused_SA_sgAdaptive_b30_K20_t0.15_nomez_population.xlsx
@@ -448,10 +448,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2.794771214727166</v>
+        <v>1.584372445946594</v>
       </c>
       <c r="D2" t="n">
-        <v>2.794771214727166</v>
+        <v>1.584372445946594</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>5.189932151734491</v>
+        <v>6.35074079006417</v>
       </c>
       <c r="D3" t="n">
-        <v>5.189932151734491</v>
+        <v>6.35074079006417</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>4.331801357700704</v>
+        <v>5.593588566581595</v>
       </c>
       <c r="D4" t="n">
-        <v>4.331801357700704</v>
+        <v>5.593588566581595</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>2.767043756661693</v>
+        <v>2.971243140865348</v>
       </c>
       <c r="D5" t="n">
-        <v>2.767043756661693</v>
+        <v>2.971243140865348</v>
       </c>
     </row>
     <row r="6">
@@ -512,10 +512,10 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>4.841623724497325</v>
+        <v>5.808732938857893</v>
       </c>
       <c r="D6" t="n">
-        <v>4.841623724497325</v>
+        <v>5.808732938857893</v>
       </c>
     </row>
     <row r="7">
@@ -528,10 +528,10 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5.13748740857682</v>
+        <v>5.232014020497039</v>
       </c>
       <c r="D7" t="n">
-        <v>5.13748740857682</v>
+        <v>5.232014020497039</v>
       </c>
     </row>
     <row r="8">
@@ -544,10 +544,10 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>3.807449491545554</v>
+        <v>4.10896839474808</v>
       </c>
       <c r="D8" t="n">
-        <v>3.807449491545554</v>
+        <v>4.10896839474808</v>
       </c>
     </row>
     <row r="9">
@@ -560,10 +560,10 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>4.297938822797055</v>
+        <v>4.109905980511727</v>
       </c>
       <c r="D9" t="n">
-        <v>4.297938822797055</v>
+        <v>4.109905980511727</v>
       </c>
     </row>
     <row r="10">
@@ -576,10 +576,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1.820492027314588</v>
+        <v>2.113653559235216</v>
       </c>
       <c r="D10" t="n">
-        <v>1.820492027314588</v>
+        <v>2.113653559235216</v>
       </c>
     </row>
     <row r="11">
@@ -592,10 +592,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3.928956737125833</v>
+        <v>3.426940176897352</v>
       </c>
       <c r="D11" t="n">
-        <v>3.928956737125833</v>
+        <v>3.426940176897352</v>
       </c>
     </row>
     <row r="12">
@@ -608,10 +608,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>2.306688174152053</v>
+        <v>2.229553653849001</v>
       </c>
       <c r="D12" t="n">
-        <v>2.306688174152053</v>
+        <v>2.229553653849001</v>
       </c>
     </row>
     <row r="13">
@@ -624,10 +624,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1.984487999124316</v>
+        <v>1.792126967656425</v>
       </c>
       <c r="D13" t="n">
-        <v>1.984487999124316</v>
+        <v>1.792126967656425</v>
       </c>
     </row>
     <row r="14">
@@ -640,10 +640,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3.062403738556654</v>
+        <v>3.172850584040361</v>
       </c>
       <c r="D14" t="n">
-        <v>3.062403738556654</v>
+        <v>3.172850584040361</v>
       </c>
     </row>
     <row r="15">
@@ -656,10 +656,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4.948156427266539</v>
+        <v>5.942155977229393</v>
       </c>
       <c r="D15" t="n">
-        <v>4.948156427266539</v>
+        <v>5.942155977229393</v>
       </c>
     </row>
     <row r="16">
@@ -672,10 +672,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>3.640663156695763</v>
+        <v>3.653176822116133</v>
       </c>
       <c r="D16" t="n">
-        <v>3.640663156695763</v>
+        <v>3.653176822116133</v>
       </c>
     </row>
   </sheetData>
